--- a/data/processed/rekap_daya_tampung_peminat_dan_sisa_kuota_2022_2026.xlsx
+++ b/data/processed/rekap_daya_tampung_peminat_dan_sisa_kuota_2022_2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ringkasan_Eksekutif" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rincian_Semua_Tahun" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tahun_2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tahun_2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tahun_2024" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tahun_2023" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Tahun_2022" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan_Eksekutif" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rincian_Semua_Tahun" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tahun_2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tahun_2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tahun_2024" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tahun_2023" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tahun_2022" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
